--- a/data/file_generation/reference/data_82/七年级标准_带等级分数公式版_res.xlsx
+++ b/data/file_generation/reference/data_82/七年级标准_带等级分数公式版_res.xlsx
@@ -1362,26 +1362,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3ED0FAC6-1291-4DC5-9C8C-9DDBD96A81B2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{179DFDC7-33B5-4206-BC95-3A4457B83289}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A4DD12D-D3E9-495B-9563-F02652110155}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D63E9F6-FEAB-4BAD-B6CB-50F5A8120519}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE9181D1-4585-48F2-A608-B8A3C2C6037B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E836E732-A20B-49CD-A90F-02825750AF48}"/>
 </file>